--- a/test/evaluation/wiki.xlsx
+++ b/test/evaluation/wiki.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0063BE7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -86,6 +91,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -624,7 +632,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -634,7 +642,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Incluye autores, década de 1980, neologismo 'creoleness', Éloge de la créolité 1989 y contexto cultural — coincide totalmente.</t>
+          <t>Incluye autores, década, neologismo y el folleto Éloge de la créolité; coincide completamente con lo esperado.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -644,12 +652,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>0.00919615</t>
+          <t>0.009222</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -723,7 +731,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -733,7 +741,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Incluye la definición esencial 'colección de obras escritas' y amplía con funciones, géneros y roles sociales — cubre totalmente.</t>
+          <t>Ofrece la definición núcleo 'colección de obras escritas' y amplía funciones y formas; cubre plenamente la respuesta esperada.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -743,12 +751,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>0.0107439</t>
+          <t>0.01076975</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -814,7 +822,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Coincide: sociedad fin de siècle en Viena, Café Griensteidl, siglo XIX; añade posición estética y miembros — cubre totalmente.</t>
+          <t>Describe el grupo Jung‑Wien, el Café Griensteidl, época y miembros; añade rechazo al naturalismo; coincide con lo esperado.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -834,12 +842,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0.0084589</t>
+          <t>0.00848475</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -906,7 +914,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -916,7 +924,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Coincide: género contemporáneo con absurdismo, sátira, grotesco y pop‑surrealismo para obras subversivas y entretenidas; añade origen editorial y escena.</t>
+          <t>Define Bizarro con absurdismo, sátira, grotesco y pop‑surrealismo y añade origen editorial y comunidad; cubre la definición esperada.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -926,12 +934,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0.0091339</t>
+          <t>0.00915975</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -1005,7 +1013,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1015,7 +1023,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Coincide: cuerpo de obras de alta cultura (literatura, música, filosofía, arte) consideradas clásicas; añade debate y ampliación del canon.</t>
+          <t>Explica el canon occidental como cuerpo de obras de alta cultura y su disputa histórica; coincide con la respuesta esperada.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1025,12 +1033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0.00884465</t>
+          <t>0.0088705</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -1093,7 +1101,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1103,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Coincide: define colon como unidad de poesía, línea cláusula en crítica textual, unidad fundamental en poesía hebrea; incluye términos relacionados.</t>
+          <t>Define colon como unidad poética y línea/cláusula en crítica textual y su uso en poesía hebrea; coincide con lo esperado.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1113,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.0087189</t>
+          <t>0.00874475</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1213,12 +1221,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1228,7 +1236,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>La lista de títulos coincide casi totalmente, pero el recuento es 38 en lugar de 39 (falta 1 artículo) — ligera discrepancia.</t>
+          <t>Lista los títulos solicitados pero indica 38 en vez de 39; cubre la mayor parte pero omite un artículo y el conteo es erróneo.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1246,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.0113014</t>
+          <t>0.01132725</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -1313,7 +1321,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1323,7 +1331,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente con los cinco artículos y sus números de categorías; ranking y cifras iguales.</t>
+          <t>Top‑5 y recuentos coinciden exactamente con la respuesta esperada; método y fuentes indicados correctamente.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1333,12 +1341,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.0109674</t>
+          <t>0.01099325</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1401,7 +1409,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1411,7 +1419,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Incluye la escuela surrealista rumana de los años 1960 y además la acepción psiquiátrica; cubre y amplía la información esperada.</t>
+          <t>Incluye la escuela surrealista rumana de los años 60 y la acepción psiquiátrica; responde completa y directamente a la pregunta.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1421,12 +1429,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0.0090444</t>
+          <t>0.00907025</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1487,7 +1495,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1497,7 +1505,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Coincide: cronistas rimados en Inglaterra, s. XIII, historias en verso con lo fabuloso; menciona Layamon's Brut y añade ejemplo posterior.</t>
+          <t>Describe cronistas rimados del s. XIII, la tradición histórica en verso y menciona Layamon's Brut; coincide plenamente con lo esperado.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1507,12 +1515,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0.0004659</t>
+          <t>0.00049175</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0.0079839</t>
+          <t>0.00800975</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1573,7 +1581,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1583,7 +1591,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Cubre la definición, periodo (c.1911–1912), objetivos (claridad, forma compacta), contraste con los simbolistas y líderes; coincide plenamente.</t>
+          <t>La respuesta cubre completamente la definición esperada (escuela modernista rusa, c.1911–12, nombre, líderes y contraste con el simbolismo).</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1593,12 +1601,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.0085939</t>
+          <t>0.0084935</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1661,12 +1669,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1676,7 +1684,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Lista sólo 7 pares frente a los 26 esperados; incluye algunos pares correctos (p.ej. Chicanafuturism–Latino Futurism) pero omite la mayoría y difiere en el recuento.</t>
+          <t>Incluye 7 pares correctos pero omite la mayoría de los 26 pares esperados; respuesta es pertinente pero incompleta.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1686,12 +1694,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0.02485515</t>
+          <t>0.02475475</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1766,7 +1774,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1776,7 +1784,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Incluye las mismas temáticas (culto a la sensibilidad, aislamiento del autor, respeto a la naturaleza, evocación/crítica del pasado), cronología y contexto; coincide.</t>
+          <t>Cubre la definición, temas, cronología y figuras principales acorde con la respuesta esperada y añade contexto útil.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1786,12 +1794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.0102719</t>
+          <t>0.0101715</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1855,7 +1863,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -1865,7 +1873,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Define la Progressive Writers' Movement como movimiento progresista en la India pre‑partición, antiimperialista y con origen histórico; coincide con lo esperado.</t>
+          <t>Describe exactamente el movimiento esperado (nombre, carácter progresista, ámbito temporal y origen) y aporta detalles coherentes.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1875,12 +1883,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.00894415</t>
+          <t>0.00884375</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -1955,7 +1963,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1965,7 +1973,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Proporciona la definición exacta (palabras en imanes, arreglo en frigorífico), historia e inventor (Dave Kapell); cubre lo solicitado.</t>
+          <t>Proporciona la definición esperada de juguete/ayuda de escritura y añade historia e metadatos del artículo, todo pertinente.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1975,12 +1983,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.00935715</t>
+          <t>0.00925675</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -2052,7 +2060,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2062,7 +2070,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Lista las 11 categorías esperadas y afirma que aparecen en ≥5 artículos del corpus; coincide exactamente con la respuesta esperada.</t>
+          <t>Lista exacta de 11 categorías solicitadas; coincide plenamente con la respuesta esperada y es directamente pertinente.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2072,12 +2080,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0.01175765</t>
+          <t>0.01165725</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -2146,7 +2154,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Ofrece la misma definición y periodo (reinado de Nerón hasta c.230 AD), finalidad retórica y figuras asociadas; coincide plenamente.</t>
+          <t>Explica el término, periodo y características clave tal como en la referencia esperada, añadiendo figuras y estilos.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2166,12 +2174,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0.0092494</t>
+          <t>0.009149</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -2237,7 +2245,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2247,7 +2255,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Los cinco artículos y sus conteos de palabras coinciden exactamente con la respuesta esperada.</t>
+          <t>Los cinco artículos y recuentos de palabras coinciden exactamente con la respuesta esperada; respuesta directa y precisa.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2257,12 +2265,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0.00841515</t>
+          <t>0.00831475</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -2342,7 +2350,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -2352,7 +2360,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Da la definición esperada de 'literatura comprometida' y añade la asociación histórica con Sartre y ejemplos; cubre totalmente.</t>
+          <t>Define la literatura comprometida como se esperaba, incluye la conexión con Sartre y detalles sobre formas y debates relevantes.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2362,12 +2370,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.0110439</t>
+          <t>0.0109435</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -2432,7 +2440,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Resume la misma idea: obras creadas o traducidas al Interlingue, menciona a Edgar de Wahl y la revista Cosmoglotta; coincide con lo esperado.</t>
+          <t>Resume correctamente que la literatura en Interlingue abarca original y traducciones, menciona revista y contexto histórico.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2452,12 +2460,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0.0004874</t>
+          <t>0.000387</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0.00849665</t>
+          <t>0.00839625</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -2529,7 +2537,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2539,7 +2547,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Definición y rasgos coinciden plenamente; la respuesta real añade detalles coherentes (relación con Realismo/Romanticismo, periodización, ámbitos artísticos).</t>
+          <t>Respuesta reproduce la definición y detalles esperados (ámbito hispánico, siglo XIX, relación con Realismo y Romanticismo).</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2549,12 +2557,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0.0100169</t>
+          <t>0.01003675</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -2615,7 +2623,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -2625,7 +2633,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Lista de secciones idéntica (Generic conventions; Examples; References). Respuesta exacta y completa.</t>
+          <t>Lista exacta de las tres secciones (Generic conventions; Examples; References), coincide totalmente con lo esperado.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2635,12 +2643,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0.00790815</t>
+          <t>0.007928</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -2721,7 +2729,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2731,7 +2739,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Todas las secciones esperadas están presentes (19 ítems) y enunciadas correctamente; coincide totalmente con el catálogo.</t>
+          <t>Incluye las 19 secciones esperadas (títulos principales y subsecciones) en contenido y cobertura completa.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2741,12 +2749,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0.0107409</t>
+          <t>0.01076075</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2815,7 +2823,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -2825,7 +2833,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Incluye todas las secciones esperadas (Origins and aims, Influence and aftermath, Jindoworobaks and Aboriginality, etc.) y añade el lead; corresponde al listado.</t>
+          <t>Cubre todas las secciones esperadas (Origins and aims, Members, Influence, críticas, referencias, enlaces) y añade el lead; pertinente y completo.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2835,12 +2843,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0.01056065</t>
+          <t>0.0105805</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -2909,7 +2917,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2919,7 +2927,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Cubre todas las partes temáticas esperadas (incluye subsecciones Postcolonialism y Feminism) pero no nombra explícitamente "References"; por lo demás completa.</t>
+          <t>Incluye casi todas las partes esperadas y subsecciones (Postcolonialism, Feminism), pero no menciona explícitamente 'References'.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2929,12 +2937,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0.0083264</t>
+          <t>0.00834625</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -3006,12 +3014,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3021,7 +3029,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Estructura y subsecciones coinciden con la lista esperada (Definition, History con sus periodos, Legacy, select lists, Works cited).</t>
+          <t>Estructura completa con subsecciones clave; omite explícitamente 'Claims of first ascents' pero cubre la mayoría de ítems esperados.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3031,12 +3039,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0.00820865</t>
+          <t>0.0082285</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -3098,7 +3106,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3108,7 +3116,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Los 11 subtemas esperados aparecen exactamente (Pre‑Columbian, Colonial, 19th, Modernism, 20th, Prose, mujeres, poetas por periodo, Further reading, See also, References).</t>
+          <t>Listado exacto de las 11 subtemas esperados (Pre-Columbian, Colonial, siglos XIX/XX, Modernism, Prose, mujeres, etc.).</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3118,12 +3126,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0.00923165</t>
+          <t>0.0092515</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -3206,7 +3214,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -3216,7 +3224,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>El resumen aborda todas las secciones esperadas (Origins, Response, Wonderland Book Award y sus categorías, Authors, Notable works, See also, References, External links).</t>
+          <t>Resumen sección por sección que corresponde a todas las entradas esperadas (Origins, Response, Wonderland Award, Authors, Notable works, etc.).</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3226,12 +3234,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0.01052365</t>
+          <t>0.0105435</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
@@ -3299,7 +3307,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3309,7 +3317,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Todos los apartados esperados están presentes (Styles, History, False writing systems, Gallery, See also, Notes, References), aunque en distinto orden.</t>
+          <t>TOC completo: Styles, History, False writing systems, Gallery, See also, Notes, References — coincide con los ítems esperados.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3319,12 +3327,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0.0079359</t>
+          <t>0.00795575</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -3385,7 +3393,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -3395,7 +3403,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Las tres categorías esperadas aparecen textualmente: Experimental film; Film styles; Poetry (coincidencia total).</t>
+          <t>Categorías listadas (Experimental film; Film styles; Poetry) coinciden exactamente con lo esperado.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3405,12 +3413,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0.0004199</t>
+          <t>0.00043975</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0.0072709</t>
+          <t>0.00729075</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -3471,7 +3479,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -3481,7 +3489,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente con la respuesta esperada; mismas cuatro categorías y hechos según el catálogo.</t>
+          <t>Lista de categorías coincide exactamente con la esperada; mismos elementos y formato informado.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3491,12 +3499,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0.00779165</t>
+          <t>0.0077675</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -3557,7 +3565,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -3567,7 +3575,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Respuesta reproduce todas las etiquetas esperadas sin omisiones; coincidencia completa con el catálogo.</t>
+          <t>Respuesta incluye todas las etiquetas esperadas para 'Mystical anarchism' y responde directamente.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3577,12 +3585,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0.0082044</t>
+          <t>0.00818025</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -3649,7 +3657,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -3659,7 +3667,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Incluye las seis etiquetas solicitadas exactamente como en la respuesta esperada; coincidencia total.</t>
+          <t>Se listan las seis categorías esperadas para 'Latin American Boom'; cumple completamente.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3669,12 +3677,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0.0078534</t>
+          <t>0.00782925</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -3735,7 +3743,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -3745,7 +3753,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Lista las tres categorías esperadas de forma exacta; corresponde plenamente al catálogo.</t>
+          <t>Las tres categorías esperadas para 'Sociology of literature' están presentes y responden la pregunta.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3755,12 +3763,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0.0082339</t>
+          <t>0.00820975</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -3821,7 +3829,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3831,7 +3839,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Relaciona las tres categorías previstas (Latin American literature; Poetry; Spanish-language literature) sin cambios.</t>
+          <t>La clasificación dada para 'Latin American poetry' coincide exactamente con la esperada.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3841,12 +3849,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0.0072844</t>
+          <t>0.00726025</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -3907,7 +3915,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -3917,7 +3925,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Presenta las cuatro categorías esperadas exactamente; completa correspondencia con la respuesta esperada.</t>
+          <t>Las cuatro categorías de 'Allusion' están completas y la respuesta es pertinente y directa.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3927,12 +3935,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0.0074074</t>
+          <t>0.00738325</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -4006,7 +4014,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -4016,7 +4024,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Incluye las trece categorías listadas en la respuesta esperada, sin omisiones; coincidencia completa.</t>
+          <t>Se listan las 13 categorías esperadas para la lista de posthumous recognition; cobertura total y relevante.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4026,12 +4034,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0.00746365</t>
+          <t>0.0074395</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -4096,7 +4104,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -4106,7 +4114,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Las cuatro categorías coinciden exactamente con la respuesta esperada; correspondencia total.</t>
+          <t>Las cuatro categorías de 'Stylistics' coinciden exactamente con la respuesta esperada.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4116,12 +4124,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0.00747615</t>
+          <t>0.007452</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -4182,7 +4190,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -4192,7 +4200,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Los tres artículos esperados aparecen tal cual (Neo-romanticism; Poetics; Pyreneanism); coincidencia completa.</t>
+          <t>Los tres artículos bajo la categoría indicada están listados tal como en la respuesta esperada.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4202,12 +4210,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0.00744815</t>
+          <t>0.007424</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -4269,7 +4277,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -4279,7 +4287,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Indica correctamente count=1 y lista "Western canon" como el único artículo sin categorías; coincide plenamente.</t>
+          <t>Coincide en conteo y artículo (Western canon) para los artículos sin categorías; responde exactamente.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4289,12 +4297,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0.0001954</t>
+          <t>0.00017125</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0.00788315</t>
+          <t>0.007859</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -4359,7 +4367,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -4369,7 +4377,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Listó exactamente las cuatro entradas esperadas y declaró 4 artículos; coincide plenamente con el gold standard.</t>
+          <t>Coincide exactamente con las cuatro entradas esperadas; formato y detalle correctos.</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4379,12 +4387,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0.00932565</t>
+          <t>0.0093475</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -4446,7 +4454,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -4456,7 +4464,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Devuelve las dos entradas esperadas (Domestic realism y Verismo); cobertura completa.</t>
+          <t>Incluye ambas entradas esperadas y aporta detalle de fuente; responde directamente.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4466,12 +4474,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0.0080859</t>
+          <t>0.00810775</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -4533,7 +4541,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -4543,7 +4551,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Incluye exactamente 'Dream vision' y 'Mennonite literature' según el catálogo; coincide totalmente.</t>
+          <t>Lista exactamente los dos artículos esperados y señala su categorización en el catálogo.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4553,12 +4561,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0.00863715</t>
+          <t>0.008659</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -4619,7 +4627,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -4629,7 +4637,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Lista 'Wiener Gruppe' y 'Young Vienna' tal como esperaba; respuesta completa y correcta.</t>
+          <t>Contiene las dos entradas esperadas para la categoría 'Austria stubs'; respuesta exacta.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4639,12 +4647,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0.00750415</t>
+          <t>0.007526</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -4706,7 +4714,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -4716,7 +4724,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Contiene justamente 'Bizarro fiction' y 'Neo-Decadence' como en la respuesta esperada.</t>
+          <t>Incluye las dos entradas esperadas para 'Fiction by genre'; respuesta directa y completa.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4726,12 +4734,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0.00872465</t>
+          <t>0.0087465</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -4794,7 +4802,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -4804,7 +4812,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Proporciona las dos entradas esperadas ('Birmingham Group (authors)', 'Rhyming Chroniclers'); coincide plenamente.</t>
+          <t>Lista las dos entradas esperadas bajo 'English history stubs'; respuesta precisa.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4814,12 +4822,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0.0085624</t>
+          <t>0.00858425</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -4883,12 +4891,12 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -4898,7 +4906,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Incluye las dos esperadas ('Chicanafuturism','Latino Futurism') pero añade dos artículos extra no requeridos, reduciendo precisión.</t>
+          <t>Incluye las dos entradas esperadas y añade dos artículos más; relevante pero ampliada respecto al oro.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4908,12 +4916,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0.0132714</t>
+          <t>0.01329325</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -5001,7 +5009,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -5011,7 +5019,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Devuelve 27 artículos correctos pero la lista esperada es mucho mayor (~100); faltan numerosas entradas clave.</t>
+          <t>Devuelve 27 artículos pero omite muchas entradas del esperado extenso; responde la categoría pero es incompleta.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5021,12 +5029,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0.0084709</t>
+          <t>0.00849275</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -5097,12 +5105,12 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -5112,7 +5120,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Solo presenta 5 artículos (todos válidos) de una larga lista esperada; cubre una pequeña fracción del gold standard.</t>
+          <t>Solo 5 artículos listados frente a las muchas entradas esperadas; listado es coherente pero claramente incompleto.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5122,12 +5130,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0.0104879</t>
+          <t>0.01050975</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -5195,17 +5203,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Incluye 4 de las 10 entradas esperadas (Postism, Wiener Gruppe, Signalism, Bizarro fiction) pero omite varias importantes.</t>
+          <t>Incluye 4 de las 10 esperadas; las seleccionadas son relevantes pero faltan varias menciones previstas.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -5215,12 +5223,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0.00040965</t>
+          <t>0.0004315</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0.01313715</t>
+          <t>0.013159</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -5295,17 +5303,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Incluye 9/22 esperados (Romanticism, Romantic literature, Neo-/Ultra-Romanticism, Novel, Condorism, Coppet, Costumbrismo, Indianism); faltan muchas entradas clave.</t>
+          <t>Incluye 9/22 artículos esperados; cubre núcleos relevantes (Romanticism, submovimientos) pero omite muchas entradas clave.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -5315,12 +5323,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0.0113994</t>
+          <t>0.01143925</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -5419,22 +5427,22 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Lista real contiene numerosos artículos de poesía relevantes (Poetry, Glossary, Outline, Latin Am. poetry, Epigram, etc.) pero omite muchas entradas esperadas.</t>
+          <t>Lista de 27 incluye varias esperadas (Poetry, Glossary, Outline) y evidencia, pero omite gran parte del listado esperado.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -5444,12 +5452,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0.01442715</t>
+          <t>0.014467</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -5522,22 +5530,22 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Solo 6 artículos coinciden (Domestic realism, Naturalism lit/theatre, Verismo, Costumbrismo, Symbolism) de un listado mucho mayor; faltan muchas entradas.</t>
+          <t>Ofrece 6 artículos relevantes a realismo pero deja fuera la mayoría de la lista esperada; respuesta parcial y pertinente.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5547,12 +5555,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0.0104624</t>
+          <t>0.01050225</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -5623,7 +5631,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -5633,7 +5641,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Reporta 5/6 esperados (falta 'Writer'); las demás coincidencias exactas y fuentes citadas.</t>
+          <t>Cubre 5/6 artículos esperados (falta 'Writer'). Respuesta es directa y basada en fragmentos recuperados.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5643,12 +5651,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0.01191665</t>
+          <t>0.0119565</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -5711,17 +5719,17 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Solo incluye 3/13 esperados (Poetry, Outline of poetry, Glossary); omite múltiples artículos que tratan la rima.</t>
+          <t>Solo 3/15 artículos esperados; son fuentes centrales que tratan la rima, pero la cobertura es claramente incompleta.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5731,12 +5739,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0.01024565</t>
+          <t>0.0102855</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -5803,7 +5811,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -5813,7 +5821,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: las cinco entradas listadas tienen 1 sección cada una según catálogo; coincide con el gold.</t>
+          <t>Coincide exactamente con los cinco artículos pedidos (cada uno con 1 sección), según el catálogo.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5823,12 +5831,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0.01129015</t>
+          <t>0.01133</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -5889,17 +5897,17 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Identificador de página coincide exactamente con el valor esperado (20295168).</t>
+          <t>El page ID proporcionado (20295168) coincide exactamente con el esperado.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5909,12 +5917,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0.00761915</t>
+          <t>0.007659</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -5975,7 +5983,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -5985,7 +5993,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Marca de descarga coincide exactamente con la esperada (2026-04-20T16:09:35Z).</t>
+          <t>La marca temporal de descarga corresponde exactamente con la esperada.</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5995,12 +6003,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0.00773315</t>
+          <t>0.007773</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -6061,7 +6069,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -6071,7 +6079,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>URL proporcionada coincide exactamente con la esperada (https://en.wikipedia.org/wiki/Shinkankakuha).</t>
+          <t>La URL proporcionada coincide exactamente con la esperada.</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -6081,12 +6089,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0.00779965</t>
+          <t>0.0078395</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -6147,7 +6155,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -6157,7 +6165,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Enlace proporcionado coincide exactamente con la esperada (https://en.wikipedia.org/wiki/Stone_and_Sky_(movement)).</t>
+          <t>La URL y metadatos indicados coinciden con la entrada esperada del catálogo.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -6167,12 +6175,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0.0003789</t>
+          <t>0.00041875</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0.0091779</t>
+          <t>0.00921775</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -6228,22 +6236,22 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Esperado 5 categorías pero respondió 3; número incorrecto, falta información clave.</t>
+          <t>Respuesta numérica directa pero incorrecta respecto al esperado (3 vs 5); omite 2 categorías.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -6253,12 +6261,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0.00799315</t>
+          <t>0.00805675</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -6319,7 +6327,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -6329,7 +6337,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: ambas indican 7 secciones.</t>
+          <t>Coincide exactamente con el valor esperado (7 secciones); respuesta clara y pertinente.</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -6339,12 +6347,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>0.00790265</t>
+          <t>0.00796625</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -6405,7 +6413,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -6415,7 +6423,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: ambas indican 135 artículos.</t>
+          <t>Coincide plenamente con el total esperado de artículos (135); responde directamente.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -6425,12 +6433,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0.0076164</t>
+          <t>0.00768</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -6491,7 +6499,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -6501,7 +6509,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: 425 categorías distintas.</t>
+          <t>Coincide exactamente con las categorías distintas esperadas (425); respuesta directa y correcta.</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -6511,12 +6519,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0.00764315</t>
+          <t>0.00770675</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -6578,7 +6586,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -6588,7 +6596,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: 'Romanticism' con 13,003 palabras.</t>
+          <t>Coincide plenamente: 'Romanticism' con 13,003 palabras; responde exactamente a la pregunta.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -6598,12 +6606,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0.0078664</t>
+          <t>0.00793</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -6664,17 +6672,17 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: promedio 1,639.1 palabras por artículo.</t>
+          <t>Coincide con el promedio esperado (1,639.1); cálculo y valor presentados correctamente.</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -6684,12 +6692,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0.0078774</t>
+          <t>0.007941</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -6751,7 +6759,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -6761,7 +6769,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: 'Writer' con 61 secciones.</t>
+          <t>Coincide exactamente: 'Writer' tiene 61 secciones; respuesta clara y pertinente.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -6771,12 +6779,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0.00739215</t>
+          <t>0.00745575</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
@@ -6847,7 +6855,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: 43 artículos con menos de 500 palabras.</t>
+          <t>Coincide con el recuento esperado (43 artículos &lt;500 palabras); respuesta directa y verificable.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6857,12 +6865,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0.01299565</t>
+          <t>0.01305925</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -6929,17 +6937,17 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Coincide: no existe artículo titular 'Magical realism'; adicionalmente se menciona como subsección.</t>
+          <t>Indica correctamente que no hay un artículo titulado 'Magical realism' y añade contexto relevante del corpus.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6949,12 +6957,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0.0084999</t>
+          <t>0.0085635</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -7023,7 +7031,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -7033,7 +7041,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Coincide: no existe artículo titulado 'Beat Generation' en el corpus.</t>
+          <t>Indica correctamente que no existe artículo titulado 'Beat Generation' en el corpus y aporta referencias relacionadas.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -7043,12 +7051,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0.00024615</t>
+          <t>0.00030975</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0.00939365</t>
+          <t>0.00945725</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -7117,7 +7125,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -7127,7 +7135,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: confirma existencia y título 'Poetry' y aporta metadata adicional.</t>
+          <t>Respuesta coincide exactamente: confirma existencia y título 'Poetry' y aporta metadata del artículo.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -7137,12 +7145,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0.0090109</t>
+          <t>0.00903275</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -7205,17 +7213,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Sólo cita 3 artículos (Western canon, Stylistics, Comedy of menace) de las ~14 esperadas; faltan la mayoría.</t>
+          <t>Responde afirmativamente y cita ejemplos, pero omite la mayoría de artículos listados en la esperada (solo 3 de ~14).</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -7225,12 +7233,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0.00975665</t>
+          <t>0.0097785</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -7291,22 +7299,22 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Menciona 2 de 3 artículos esperados (Latin American poetry; Stone and Sky), omite 'Outline of poetry'.</t>
+          <t>Identifica a Pablo Neruda en dos artículos correctamente, pero omite 'Outline of poetry' presente en la esperada.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -7316,12 +7324,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>0.0113534</t>
+          <t>0.01137525</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -7396,7 +7404,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -7406,7 +7414,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Lista completa y cuenta=14 coinciden exactamente con la esperada.</t>
+          <t>Lista exhaustiva y exacta de los 14 títulos con paréntesis, coincide plenamente con la respuesta esperada.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -7416,12 +7424,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>0.01682765</t>
+          <t>0.0168495</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -7617,7 +7625,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -7627,7 +7635,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Proporciona la lista completa de 135 títulos, coincidente con la esperada.</t>
+          <t>Proporciona la lista completa de 135 títulos tal como esperaba la respuesta; completa y pertinente.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -7637,12 +7645,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0.0120154</t>
+          <t>0.01203725</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -7837,7 +7845,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -7847,7 +7855,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Entrega el catálogo completo de 135 artículos, igual que el esperado.</t>
+          <t>Entrega el catálogo completo de 135 artículos, cumpliendo exactamente la petición.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7857,12 +7865,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0.0098684</t>
+          <t>0.00989025</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -7936,7 +7944,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -7946,7 +7954,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Incluye casi todas las entradas pero duplica 'Parnassianism' y omite 'Postism' (error menor).</t>
+          <t>Lista la mayoría de títulos con P pero repite 'Parnassianism' y omite 'Postism'; respuesta útil pero con error menor.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7956,12 +7964,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0.0093799</t>
+          <t>0.00940175</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -8030,7 +8038,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
@@ -8040,7 +8048,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: par 'Chicanafuturism' y 'Latino Futurism' con 8 categorías compartidas listadas.</t>
+          <t>Identifica correctamente el par y el conteo (Chicanafuturism, Latino Futurism) y enumera las 8 categorías compartidas.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -8050,12 +8058,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0.01296565</t>
+          <t>0.0129875</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -8116,7 +8124,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -8126,7 +8134,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: ambas entradas ('Romantic literature', 'Ultra-Romanticism') aparecen.</t>
+          <t>Responde exactamente: ambos artículos ('Romantic literature', 'Ultra-Romanticism') comparten la categoría solicitada.</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -8136,12 +8144,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>0.0078719</t>
+          <t>0.00789375</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -8202,7 +8210,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -8212,7 +8220,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: 'Birmingham Group (authors)' y 'Rhyming Chroniclers' están presentes.</t>
+          <t>Identifica correctamente las dos entradas bajo 'English history stubs' según el catálogo; respuesta directa y correcta.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -8222,12 +8230,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0.0004809</t>
+          <t>0.00050275</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0.00762565</t>
+          <t>0.0076475</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -8291,17 +8299,17 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real confirma que el artículo menciona poesía y poetas, aporta citas y fuentes que apoyan el hecho.</t>
+          <t>Afirma 'sí' y aporta ejemplos y fuentes que muestran que el artículo menciona poesía y poetas.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -8311,12 +8319,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>0.0089939</t>
+          <t>0.0088495</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -8378,17 +8386,17 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Afirma explícitamente que Neo‑Decadence se refiere al Decadent movement y aporta fragmentos y metadatos; coincide plenamente.</t>
+          <t>Confirma explícitamente que Neo‑Decadence refiere al Decadent movement y aporta fragmentos y fuentes.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -8398,12 +8406,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0.00906415</t>
+          <t>0.00891975</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -8478,17 +8486,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Describe la conexión conceptual entre Poetry y Western canon con ejemplos y hechos documentados; cubre lo esperado por completo.</t>
+          <t>Describe con detalle las conexiones conceptuales entre Poetry y Western canon, citando secciones y hechos.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -8498,12 +8506,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0.01020115</t>
+          <t>0.01005675</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -8565,7 +8573,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -8575,7 +8583,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Indica que Thơ mới menciona 'poetry' en título y en el texto, con ejemplos; cumple exactamente con la expectativa.</t>
+          <t>Confirma la presencia del término 'poetry' en título y cuerpo del artículo con ejemplos textuales.</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -8585,12 +8593,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0.0090909</t>
+          <t>0.0089465</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -8656,17 +8664,17 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Muestra que Jadid incluyó actividades de escritura y autores (ej. Fitrat), estableciendo la relación con 'Writer' como se esperaba.</t>
+          <t>Muestra evidencia clara de actividades de escritura y un miembro identificado como escritor Jadid; conecta con 'writer'.</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -8676,12 +8684,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0.0091919</t>
+          <t>0.0090475</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -8747,7 +8755,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
@@ -8757,7 +8765,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Lista y recuentos coinciden exactamente con la respuesta esperada (mismos títulos y conteos de palabras).</t>
+          <t>Lista exacta de cinco artículos y recuentos de palabras coincidiendo con el esperado y la fuente del catálogo.</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -8767,12 +8775,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>0.00866165</t>
+          <t>0.00851725</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -8829,12 +8837,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
@@ -8844,7 +8852,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Lista extensa incluye casi todos los títulos esperados y varios adicionales; solo omite 'Latin American poetry' de la lista esperada.</t>
+          <t>Proporciona una lista muy amplia (91) que incluye la mayoría de los movimientos esperados; supera la lista esperada.</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -8854,12 +8862,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>0.0109129</t>
+          <t>0.0107685</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -8945,7 +8953,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -8955,7 +8963,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Cuenta y lista idénticas a las esperadas (24 títulos y mismos nombres); coincide plenamente.</t>
+          <t>Coincide exactamente: cuenta=24 y lista de 24 títulos idéntica a la esperada, con desglose por vocal inicial.</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -8965,12 +8973,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>0.01099765</t>
+          <t>0.01085325</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
@@ -9048,7 +9056,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -9058,7 +9066,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Solo 9 artículos listados frente a ~15 esperados; faltan entradas clave como 'Poetry', 'Stylistics', 'British Poetry Revival', etc.</t>
+          <t>Devuelve 9 artículos que mencionan Oxford Univ. Press pero omite varios esperados; respuesta relevante pero incompleta.</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -9068,12 +9076,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0.01406065</t>
+          <t>0.01391625</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -9145,22 +9153,22 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="L91" s="5" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Incluye 8 de 11 artículos esperados (p. ej. falta 'Decadent movement', 'Interlingue literature' y 'Latin American Boom'); cobertura parcial.</t>
+          <t>Lista 8 artículos que referencian Poe (varios coinciden con lo esperado) pero faltan ~3 entradas esperadas.</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -9170,12 +9178,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0.0006894</t>
+          <t>0.000545</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>0.01182765</t>
+          <t>0.01168325</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -9240,22 +9248,22 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Coincide en 5 de 9 artículos esperados (Writer, Latin American Boom, Dream vision, Liberature, Western canon) pero da conteo 5 en lugar de 9 y omite 4 artículos.</t>
+          <t>Contiene 5 de 9 artículos esperados (parcialmente correcto). Responde directamente a la pregunta pero omite varios artículos.</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -9265,12 +9273,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>0.0113699</t>
+          <t>0.0114375</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -9343,7 +9351,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -9353,7 +9361,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Lista 6 de las 8 esperadas y afirma 6; faltan dos artículos respecto a la esperada, por lo que cubre la mayor parte pero no todo.</t>
+          <t>Lista 6 de 8 artículos esperados (cubre la mayoría). Responde claramente con número y listado, aunque es incompleto.</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -9363,12 +9371,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>0.0162964</t>
+          <t>0.016364</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
@@ -9426,22 +9434,22 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>La esperada indica referencia mutua; la real afirma solo Abbaye→Unanimism (asimétrica). Contradicción importante respecto a referencia bidireccional.</t>
+          <t>Contradice la expectativa de referencia mutua (afirma asimetría). Contesta la pregunta y explica la asimetría de forma coherente.</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -9451,12 +9459,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>0.0092099</t>
+          <t>0.0092775</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
@@ -9518,22 +9526,22 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>La esperada indica conexión mutua; la real niega evidencia de enlace bidireccional entre Allusion y Poetry, contradiciendo la respuesta esperada.</t>
+          <t>Declara que no hay conexión bidireccional, contrario al esperado. Respuesta es directa y justificada respecto a la pregunta.</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -9543,12 +9551,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0.01119515</t>
+          <t>0.01126275</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr"/>
@@ -9605,22 +9613,22 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Esperado 27 pares mutuamente referenciados; la real afirma 0, negando por completo la información esperada.</t>
+          <t>Afirmación de 0 pares es fuertemente discrepante con 27 esperados. Responde la pregunta pero contradice la referencia esperada.</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -9630,12 +9638,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>0.0092174</t>
+          <t>0.009285</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
@@ -9704,14 +9712,14 @@
           <t>80</t>
         </is>
       </c>
-      <c r="L97" s="4" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Esperado indica cadena Abbaye→Poetry→Allusion; la real niega cualquier intermediario en el corpus, contradiciendo la respuesta esperada.</t>
+          <t>Indica que no existe un intermediario en el corpus; difiere del encadenamiento esperado. Respuesta directa y explicada.</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -9721,12 +9729,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0.0148119</t>
+          <t>0.0148795</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
@@ -9789,17 +9797,17 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Esperado propone 'Poetry' como intermedio; la real propone 'Symbolism (movement)', por tanto no coincide con la respuesta esperada.</t>
+          <t>Propone 'Symbolism' como intermediario en vez de 'Poetry' (incorrecto según esperado). Responde la pregunta pero con error factual.</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -9809,12 +9817,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>0.01002865</t>
+          <t>0.01009625</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -9876,7 +9884,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
@@ -9886,7 +9894,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>La real incluye las 7 categorías esperadas y añade 'Literary movements' extra; cubre completamente la lista esperada con un añadido menor.</t>
+          <t>Incluye las 7 categorías esperadas más una adicional; alta cobertura y respuesta muy pertinente.</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -9896,12 +9904,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>0.00797165</t>
+          <t>0.00803925</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
@@ -9968,7 +9976,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -9978,7 +9986,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>La real contiene las 4 categorías esperadas y suma 'Literary movements'; coincide con todas las categorías esperadas salvo una adición.</t>
+          <t>Enumera las categorías esperadas y añade 'Literary movements'; cubre esencialmente la información solicitada.</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -9988,12 +9996,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>0.00885615</t>
+          <t>0.00892375</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -10057,7 +10065,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -10067,7 +10075,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Esperado 'Achim von Arnim'; la real lista otros nombres (Germaine de Staël, Poe, Maturin, Hawthorne) sin incluir el esperado: no hay coincidencia.</t>
+          <t>Ninguna coincidencia con la entidad esperada; aunque lista nombres presentes en ambos artículos, no ofrece el nombre correcto.</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -10077,12 +10085,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0.0003609</t>
+          <t>0.0004285</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>0.00857515</t>
+          <t>0.00864275</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
@@ -10266,22 +10274,22 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Indica que es novela y editorial/fecha, pero omite autor (SenLinYu), el título en español y los géneros (horror, fantasía oscura, romance gótico).</t>
+          <t>Indica que es una novela y la editorial/año, pero omite autora (SenLinYu), el título completo en español y los géneros (horror, fantasía oscura, romance gótico).</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -10291,12 +10299,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>0.0093245</t>
+          <t>0.0093145</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -10357,7 +10365,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -10367,7 +10375,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Cubre autor (Jason Pargin/David Wong), cronología (web 2001, manuscrito 2004, bolsillo 2007), géneros, secuelas y adaptación cinematográfica.</t>
+          <t>Cubre autor, seudónimo, publicación online desde 2001, ediciones impresas (2007, 2009), tono lovecraftiano y adaptación cinematográfica: coincide totalmente y es relevante.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -10377,12 +10385,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>0.00960225</t>
+          <t>0.00959225</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -10451,7 +10459,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -10461,7 +10469,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: define bloqueo del escritor, causas, duración, ejemplos, estrategias de afrontamiento y referencias.</t>
+          <t>Define el bloqueo del escritor, causas, duración, ejemplos históricos y estrategias de afrontamiento; coincide con la respuesta esperada y responde directamente.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10471,12 +10479,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0.009501</t>
+          <t>0.009491</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -10540,7 +10548,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -10550,7 +10558,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Describe correctamente la gnómica como género de máximas en verso, su carácter sapiencial y raíces históricas y culturales.</t>
+          <t>Da la definición esencial: poesía de máximas en verso, añade contexto sapiencial e históricos; cubre la información esperada y responde claramente.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10560,12 +10568,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0.009499</t>
+          <t>0.009489</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -10633,7 +10641,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -10643,7 +10651,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: define el misterio histórico como subgénero entre ficción histórica y novela de misterio y aporta antecedentes y variaciones.</t>
+          <t>Explica que es un subgénero que une ficción histórica y novela de misterio, con características, orígenes y ejemplos: coincide plenamente y es pertinente.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10653,12 +10661,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0.01095775</t>
+          <t>0.01094775</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -10720,7 +10728,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -10730,7 +10738,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: indica fundación en mayo de 1965 por Roberto Jorge Santoro y Marcos Silber y añade datos editoriales y sedes.</t>
+          <t>Indica fundación en mayo de 1965 por Santoro y Silber, origen del nombre y añade sedes y publicaciones; coincide y responde exactamente.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10740,12 +10748,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.0094465</t>
+          <t>0.0094365</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -10849,7 +10857,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -10859,7 +10867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Lista casi completa pero difiere en el recuento (43 vs 44) y parece omitir un título; por lo demás coincide en los ítems mostrados.</t>
+          <t>Lista casi todos los títulos pedidos y cumple el formato, pero el conteo difiere (43 vs 44) y falta un artículo para ser exhaustiva.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10869,12 +10877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.01614525</t>
+          <t>0.01613525</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -10941,7 +10949,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -10951,7 +10959,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente en los cinco artículos y sus números de categorías, con el mismo orden y valores.</t>
+          <t>Proporciona los cinco artículos con sus números de categorías exactamente como en la respuesta esperada; correcto y relevante.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10961,12 +10969,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.0132245</t>
+          <t>0.0132145</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -11027,7 +11035,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -11037,7 +11045,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Definición fiel: novela ensamblada a partir de cuentos publicados separadamente, menciona edición y recursos de unificación y origen del término.</t>
+          <t>Define el fix-up perfectamente: novela ensamblada a partir de cuentos, con edición para coherencia y posible narración marco; coincide y es claro.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11047,12 +11055,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0.00907525</t>
+          <t>0.00906525</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -11124,7 +11132,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -11134,7 +11142,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: indica que Bookstagram proviene de 'books' + 'Instagram' y aporta definición y funcionalidades de la comunidad.</t>
+          <t>Describe Bookstagram y su origen etimológico (books+Instagram), tipo de contenido y impacto; cubre la definición esperada y es pertinente.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11144,12 +11152,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0.000452</t>
+          <t>0.000442</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0.00959175</t>
+          <t>0.00958175</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -11212,7 +11220,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -11222,7 +11230,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Definición prácticamente idéntica; añade detalle coherente sobre lo sobrenatural y la vida interior, sin discrepancias.</t>
+          <t>Respuesta prácticamente idéntica a la esperada; incluye el mismo contenido y matices adicionales coherentes.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11232,12 +11240,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.00971175</t>
+          <t>0.00970175</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -11313,7 +11321,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -11323,7 +11331,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Incluye 14 pares correctos pero omite 8 pares del esperado y difiere en el recuento total (14 vs 22). Cobertura parcial.</t>
+          <t>Lista parcial: devuelve 14 pares frente a 22 esperados; varios pares faltan pese a coincidir algunos elementos.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11333,12 +11341,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0.024578</t>
+          <t>0.024568</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -11407,7 +11415,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -11417,7 +11425,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Explica claramente que la prosa poética es un tipo lírico en prosa, coincide con la definición esperada y añade contexto histórico.</t>
+          <t>Define la prosa poética como en la referencia y añade historia y ejemplos, respondiendo exactamente.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11427,12 +11435,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.01057775</t>
+          <t>0.01056775</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -11493,7 +11501,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -11503,7 +11511,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Describe correctamente la novela Extinción (título alemán, autor, forma y contenido), coincide totalmente con lo esperado.</t>
+          <t>Describe la novela, su título en alemán, autor, argumento y estilo; cubre la información esperada completamente.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11513,12 +11521,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.00956275</t>
+          <t>0.00955275</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -11623,7 +11631,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -11633,7 +11641,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Incluye la definición exacta de poesía dub y añade metadatos y lista de poetas; cubre plenamente la información esperada.</t>
+          <t>Incluye la definición esperada y añade metadatos y lista de poetas; responde plenamente a la pregunta.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11643,12 +11651,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.012438</t>
+          <t>0.012428</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -11723,7 +11731,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -11733,7 +11741,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Lista exhaustiva y recuentos coincidentes con el esperado (14 categorías), nombres y cifras congruentes (ligera variación de etiqueta menor).</t>
+          <t>Lista exhaustiva que coincide con las categorías esperadas (nombra 14 entradas y recuentos), responde correctamente.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11743,12 +11751,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0.01779125</t>
+          <t>0.01778125</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -11821,7 +11829,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -11831,7 +11839,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Definición y características del positivismo coinciden con lo esperado, con ampliaciones coherentes sobre variantes e historia.</t>
+          <t>Explica el positivismo con los mismos puntos clave (verificación, rechazo de metafísica, Comte) y variantes; completo y pertinente.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11841,12 +11849,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0.0101795</t>
+          <t>0.0101695</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -11913,7 +11921,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -11923,7 +11931,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Misma lista y mismos recuentos de palabras en el mismo orden; coincide plenamente con lo esperado.</t>
+          <t>Coincide exacta y ordenadamente con los cinco artículos y sus recuentos de palabras esperados.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11933,12 +11941,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0.010127</t>
+          <t>0.010117</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -12020,7 +12028,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -12030,7 +12038,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Describe la sede en KU Leuven y la misión/historia y fondos tal como en el esperado; información consistente y completa.</t>
+          <t>Describe los Archivos Husserl, sede en KU Leuven y detalles históricos y de fondos que concuerdan con lo esperado.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12040,12 +12048,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.01096175</t>
+          <t>0.01095175</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -12109,7 +12117,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -12119,7 +12127,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Definición concisa y coincidente: unidad formada en el tiempo, reconocida por sus hablantes y con variedades internas, como se pide.</t>
+          <t>Da la definición esperada de lengua histórica, añade breve aclaración sobre variedades y ejemplos; responde directamente.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12129,12 +12137,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0.0004495</t>
+          <t>0.0004395</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0.00878375</t>
+          <t>0.00877375</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -12206,7 +12214,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -12216,7 +12224,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Incluye la definición esperada (Edith Pargeter/Ellis Peters) y añade datos verificados (n.º de novelas, fechas, ambientación, protagonista y adaptaciones).</t>
+          <t>Incluye la definición esperada (Edith Pargeter/Ellis Peters) y además detalles correctos sobre novelas, ambientación, protagonista y adaptaciones.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12226,12 +12234,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0.010514</t>
+          <t>0.01057225</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -12292,7 +12300,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -12302,7 +12310,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>La respuesta lista exactamente las mismas ocho secciones solicitadas (mismo conjunto de apartados).</t>
+          <t>Lista exactamente las ocho secciones solicitadas y cita el catálogo/metadatos como fuente.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12312,12 +12320,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0.00853275</t>
+          <t>0.008591</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -12378,7 +12386,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -12388,7 +12396,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: Biografía, Libros y Referencias aparecen tal cual en la respuesta real.</t>
+          <t>Coincide exactamente con los tres apartados indicados: Biografía; Libros; Referencias.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12398,12 +12406,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0.007932</t>
+          <t>0.00799025</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -12475,22 +12483,22 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Cubre las principales áreas (tipos, proceso, soledad, motivaciones, controversia, protección y premios) pero no enumera todos los subtipos detallados del listado esperado.</t>
+          <t>Resume bien los temas principales y muchos subtítulos (tipos, proceso, soledad), pero no enumera exhaustivamente todas las secciones esperadas.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12500,12 +12508,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0.01035</t>
+          <t>0.01040825</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -12566,7 +12574,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -12576,7 +12584,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>La respuesta incluye exactamente las cinco secciones solicitadas en el artículo: En español; En otros idiomas; Véase también; Referencias; Enlaces externos.</t>
+          <t>Incluye las cinco secciones esperadas (mismas etiquetas aunque el orden difiera en la respuesta real).</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12586,12 +12594,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0.0086165</t>
+          <t>0.00867475</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -12654,22 +12662,22 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Incluye lead, Orígenes, Popularización y Variaciones pero omite secciones esperadas como Premios, Referencias y la lista de detectives históricos ficticios.</t>
+          <t>Da lead y cuatro secciones (Orígenes, Popularización, Variaciones, Enlaces) pero omite 'Premios', 'Referencias' y la 'Lista de detectives históricos ficticios'.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12679,12 +12687,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0.0113005</t>
+          <t>0.01135875</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -12750,12 +12758,12 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -12765,7 +12773,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Cubre la mayor parte de los subtemas esperados (orígenes, épocas, frecuencia, informes, revistas, cronología, prohibición); faltan menciones explícitas menores como 'Suplementos' o 'Referencias'.</t>
+          <t>Cubre la mayoría de subtemas clave (orígenes, épocas, informes, revistas, cronología, represión) pero no menciona explícitamente 'Suplementos' ni 'Referencias'.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12775,12 +12783,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0.0095935</t>
+          <t>0.00965175</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -12848,7 +12856,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -12858,7 +12866,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: existe lead además de las dos secciones esperadas Bibliografía y Referencias.</t>
+          <t>Incluye el lead y las dos secciones esperadas: 'Bibliografía' y 'Referencias', con detalle sobre el contenido.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12868,12 +12876,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0.01000575</t>
+          <t>0.010064</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
@@ -12937,7 +12945,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -12947,7 +12955,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>La respuesta lista las dos secciones esperadas: Poetas dub significativos y Referencias.</t>
+          <t>Presenta exactamente las dos secciones del índice: 'Poetas dub significativos' y 'Referencias'.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12957,12 +12965,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0.008732</t>
+          <t>0.00879025</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -13027,12 +13035,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -13042,7 +13050,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Incluye definición, origen, influencia y listado de autores y enlaces externos; sin embargo no menciona la sección 'Véase también' esperada.</t>
+          <t>Describe definición, origen, lista de autores y enlaces externos; omite 'Véase también' que aparecía en la respuesta esperada.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13052,12 +13060,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0.00041675</t>
+          <t>0.000475</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0.00933025</t>
+          <t>0.0093885</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -13119,7 +13127,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -13129,7 +13137,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Lista real contiene exactamente las cuatro secciones esperadas, solo cambia el orden.</t>
+          <t>Lista exacta de las cuatro secciones solicitadas; coincide totalmente con la esperada.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13139,12 +13147,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0.00966075</t>
+          <t>0.00964875</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -13205,7 +13213,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -13215,7 +13223,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real coincide exactamente con la categoría esperada: Poesía.</t>
+          <t>Respuesta única y exacta: 'Poesía' coincide completamente con la esperada.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13225,12 +13233,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0.0087715</t>
+          <t>0.0087595</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -13291,7 +13299,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -13301,7 +13309,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Las cuatro categorías esperadas aparecen textualmente en la respuesta real.</t>
+          <t>Las cuatro categorías esperadas están todas presentes y correctamente listadas.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13311,12 +13319,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0.00817575</t>
+          <t>0.00816375</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -13377,7 +13385,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -13387,7 +13395,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>La respuesta incluye ambas categorías esperadas: Arte de Perú y Poesía.</t>
+          <t>Ambas categorías esperadas ('Arte de Perú', 'Poesía') aparecen correctamente.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13397,12 +13405,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0.00836125</t>
+          <t>0.00834925</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -13463,7 +13471,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -13473,7 +13481,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Las cinco etiquetas esperadas aparecen en la respuesta real sin omisiones.</t>
+          <t>Las cinco etiquetas solicitadas están todas presentes y correctamente listadas.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13483,12 +13491,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0.008621</t>
+          <t>0.008609</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -13549,7 +13557,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -13559,7 +13567,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Las cinco categorías esperadas están presentes ("Literatura modernista" equivalente a "Literatura del Modernismo").</t>
+          <t>Incluye las mismas cinco categorías; 'Literatura modernista' corresponde a 'Literatura del Modernismo'.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13569,12 +13577,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0.01612675</t>
+          <t>0.01611475</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -13631,12 +13639,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -13646,7 +13654,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Faltó "Novelas adaptadas al teatro" y "Novelas" aparece duplicada; por lo demás coincide con la mayor parte.</t>
+          <t>Lista la mayoría correcta pero duplica 'Novelas' y omite 'Novelas adaptadas al teatro', por eso no es perfecto.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13656,12 +13664,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0.0083215</t>
+          <t>0.0083095</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -13722,7 +13730,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -13732,7 +13740,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Ambas categorías esperadas (Literatura; Traducción) están presentes en la respuesta real.</t>
+          <t>Ambas categorías ('Literatura', 'Traducción') aparecen claramente; responde exactamente a la pregunta.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13742,12 +13750,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0.008789</t>
+          <t>0.008777</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -13808,7 +13816,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -13818,7 +13826,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Las tres categorías esperadas aparecen exactamente en la respuesta real.</t>
+          <t>Las tres categorías esperadas ('Libros por tipo', 'Literatura', 'Magia') están todas presentes.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -13828,12 +13836,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0.008455</t>
+          <t>0.008443</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -13894,7 +13902,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -13904,7 +13912,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: count=0 y lista vacía, la respuesta indica que no hay artículos sin categoría.</t>
+          <t>Respuesta indica correctamente que no hay artículos sin categoría (count 0, lista vacía), coincide con la esperada.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -13914,12 +13922,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0.00030075</t>
+          <t>0.00028875</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0.01250075</t>
+          <t>0.01248875</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -13980,7 +13988,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -13990,7 +13998,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: los tres artículos esperados aparecen tal cual en la respuesta real.</t>
+          <t>Respuesta lista exactamente los tres artículos esperados y confirma su pertenencia a la categoría.</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14000,12 +14008,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0.00893875</t>
+          <t>0.008963</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -14069,7 +14077,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -14079,7 +14087,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: los tres títulos esperados están listados en la respuesta real.</t>
+          <t>Coincide íntegramente con la lista esperada y es directamente relevante a la petición.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14089,12 +14097,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0.008502</t>
+          <t>0.00852625</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -14169,17 +14177,17 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Solo coincide 'Drama' de las cinco entradas esperadas; faltan Bizarro, Fix-up, Misterio histórico y Novela paralela.</t>
+          <t>Da un panorama amplio de géneros (muy relevante) pero solo incluye 'drama' de los cinco títulos esperados; omite bizarro, fix-up, misterio histórico y novela paralela.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -14189,12 +14197,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0.0105365</t>
+          <t>0.01056075</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -14255,7 +14263,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -14265,7 +14273,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: los tres artículos esperados aparecen en la respuesta real.</t>
+          <t>Lista exactamente los tres artículos esperados y confirma su pertenencia a la categoría.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -14275,12 +14283,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0.0083105</t>
+          <t>0.00833475</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -14343,7 +14351,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -14353,7 +14361,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: ambos artículos esperados están presentes en la respuesta real.</t>
+          <t>Respuesta coincide plenamente con los dos artículos esperados y atiende la pregunta de forma directa.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -14363,12 +14371,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0.00958575</t>
+          <t>0.00961</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -14429,7 +14437,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -14439,7 +14447,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: los dos títulos esperados aparecen en la respuesta real.</t>
+          <t>Lista exactamente los dos artículos esperados bajo 'Literatura juvenil' y es totalmente pertinente.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -14449,12 +14457,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0.00893975</t>
+          <t>0.008964</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -14517,7 +14525,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -14527,7 +14535,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: ambos artículos esperados figuran en la respuesta real.</t>
+          <t>Coincide íntegramente con la lista esperada de colecciones y responde directamente.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -14537,12 +14545,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0.00822175</t>
+          <t>0.008246</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -14603,7 +14611,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -14613,7 +14621,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: los dos poetas esperados están listados en la respuesta real.</t>
+          <t>Lista exactamente los dos poetas esperados; respuesta precisa y relevante.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -14623,12 +14631,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0.0107525</t>
+          <t>0.01077675</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -14691,7 +14699,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -14701,7 +14709,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia exacta: ambos artículos esperados aparecen en la respuesta real.</t>
+          <t>Contiene exactamente los dos artículos esperados bajo Literatura de Colombia; respuesta directa y correcta.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -14711,12 +14719,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0.00861325</t>
+          <t>0.0086375</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -14780,17 +14788,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>La respuesta incluye 4 de 6 artículos esperados (faltan 'Cosmopolitismo en la literatura' y 'Post-Boom').</t>
+          <t>Lista cuatro artículos que mencionan a García Márquez (correctos) pero omite 'Cosmopolitismo en la literatura' y 'Post-Boom', no es exhaustiva.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -14800,12 +14808,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0.0002945</t>
+          <t>0.00031875</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0.0112125</t>
+          <t>0.01123675</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -14867,17 +14875,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Solo identifica 2 de 10 artículos esperados (Ultraísmo y Boom latinoamericano); omite el resto.</t>
+          <t>Incluye solo 2 de los 10 artículos esperados (Ultraísmo y Boom); son correctos pero la respuesta es claramente incompleta.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -14887,12 +14895,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0.01066375</t>
+          <t>0.01057575</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -14958,17 +14966,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Solo devuelve 2 artículos (Cosmopolitismo, Literatura del absurdo) de una lista amplia esperada; faltan muchos.</t>
+          <t>Reporta 2 artículos que tratan el surrealismo; son válidos pero faltan muchos artículos esperados.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -14978,12 +14986,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0.012033</t>
+          <t>0.011945</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -15050,17 +15058,17 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Lista 27 artículos, muchos coinciden con la esperada (varias novelas), pero omite gran parte de la lista larga esperada.</t>
+          <t>Lista 27 artículos (muchos son novelas en sí) y 3 generales; cubre bastante pero omite gran parte de la lista esperada.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -15070,12 +15078,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0.01472975</t>
+          <t>0.01464175</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -15154,22 +15162,22 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Incluye 23 títulos con 'poesía' exacta, cubre varios esperados pero deja fuera numerosos artículos de la lista esperada.</t>
+          <t>Devuelve 23 títulos con la palabra exacta 'poesía'; respuesta coherente y directa pero no tan exhaustiva como la lista esperada.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -15179,12 +15187,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0.01413625</t>
+          <t>0.01404825</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -15265,22 +15273,22 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Proporciona 11 artículos relacionados con el romanticismo de 23 esperados; cubre aspectos pero omite varios elementos clave.</t>
+          <t>Incluye 11 artículos relevantes sobre romanticismo; cubre parte importante pero faltan varios ítems esperados.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -15290,12 +15298,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0.0144475</t>
+          <t>0.0143595</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -15361,7 +15369,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -15371,7 +15379,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente con los 5 artículos y el número de secciones indicado, con desempate documentado.</t>
+          <t>Coincide exactamente con la lista esperada de cinco artículos con 1 sección; desempate alfabético aplicado, tal como se indicó.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -15381,12 +15389,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0.011031</t>
+          <t>0.010943</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -15447,7 +15455,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -15457,7 +15465,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>El pageid devuelto (11408367) coincide exactamente con la respuesta esperada.</t>
+          <t>El pageid proporcionado (11408367) coincide exactamente con el esperado.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -15467,12 +15475,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0.0084935</t>
+          <t>0.0084055</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -15534,7 +15542,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -15544,7 +15552,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Idioma indicado 'Español' corresponde exactamente al código esperado 'es'.</t>
+          <t>Indica 'Español' como idioma, equivalente a 'es' esperado; respuesta correcta y directa.</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -15554,12 +15562,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0.00848325</t>
+          <t>0.00839525</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -15620,7 +15628,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -15630,7 +15638,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>La marca de tiempo de descarga coincide exactamente con la esperada.</t>
+          <t>La marca temporal de descarga coincide exactamente con la esperada.</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -15640,12 +15648,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0.0083855</t>
+          <t>0.0082975</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -15706,7 +15714,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -15716,7 +15724,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>La URL devuelta coincide exactamente con la esperada.</t>
+          <t>La URL del artículo coincide exactamente con la esperada (https://es.wikipedia.org/wiki/Chbab_Srey).</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -15726,12 +15734,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0.00051575</t>
+          <t>0.00042775</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0.00854825</t>
+          <t>0.00846025</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -15792,7 +15800,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -15802,7 +15810,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>La URL proporcionada coincide exactamente con la esperada; incluye además metadatos y fuente.</t>
+          <t>Enlace exacto proporcionado; coincide totalmente con la URL esperada y ofrece metadatos.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -15812,12 +15820,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0.00839525</t>
+          <t>0.0084075</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -15878,17 +15886,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real indica 3 categorías pero la esperada es 4: dato numérico clave incorrecto.</t>
+          <t>Responde directamente pero contradice la respuesta esperada (indica 3 en lugar de 4 categorías).</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -15898,12 +15906,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>0.009608</t>
+          <t>0.00962025</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -15964,7 +15972,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -15974,7 +15982,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Ambas indican exactamente 187 artículos; detalle y fuente coinciden.</t>
+          <t>Número total de artículos coincide exactamente con la esperada y responde la pregunta de forma directa.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -15984,12 +15992,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0.00788125</t>
+          <t>0.0078935</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -16050,7 +16058,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -16060,7 +16068,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente en 353 categorías distintas; fuente y valor idénticos.</t>
+          <t>Coincide exactamente en el conteo de categorías distintas; respuesta directa y pertinente.</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -16070,12 +16078,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0.00810925</t>
+          <t>0.0081215</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -16136,7 +16144,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -16146,7 +16154,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Artículo y número de palabras coinciden: 'Literatura del naturalismo' — 9403 palabras.</t>
+          <t>Artículo y número de palabras coinciden exactamente con la respuesta esperada; completo y pertinente.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -16156,12 +16164,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0.00803625</t>
+          <t>0.0080485</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -16222,7 +16230,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -16232,7 +16240,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>La media indicada (1265.7) coincide exactamente con la esperada y se justifica con cálculos.</t>
+          <t>Media de palabras igual a la esperada; cálculo y cifra coinciden y responden claramente.</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -16242,12 +16250,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0.008247</t>
+          <t>0.00825925</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -16308,7 +16316,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -16318,7 +16326,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Identifica correctamente el artículo 'Escritor' como el que tiene más secciones (37).</t>
+          <t>Identifica el artículo correcto y el detalle indica que tiene 37 secciones, coincidente y pertinente.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -16328,12 +16336,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0.00863975</t>
+          <t>0.008652</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -16394,7 +16402,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
@@ -16404,7 +16412,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Top 5 de categorías y sus recuentos coinciden exactamente con la respuesta esperada.</t>
+          <t>Top5 de categorías y sus conteos coinciden exactamente con la respuesta esperada; directo y completo.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -16414,12 +16422,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0.00811975</t>
+          <t>0.008132</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -16481,7 +16489,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -16491,7 +16499,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Confirma existencia y título 'Realismo mágico' y ofrece metadatos y contenidos concordantes.</t>
+          <t>Confirma existencia y título del artículo, aporta metadatos y fragmentos; cubre lo esperado y responde bien.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -16501,12 +16509,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0.01044825</t>
+          <t>0.0104605</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -16576,7 +16584,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -16586,7 +16594,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Confirma existencia y título 'Boom latinoamericano' con URL y metadatos que coinciden.</t>
+          <t>Confirma existencia y título 'Boom latinoamericano' con metadatos y fragmentos; coincide y es relevante.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -16596,12 +16604,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0.0002295</t>
+          <t>0.00024175</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0.00923775</t>
+          <t>0.00925</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -16670,7 +16678,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -16680,7 +16688,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real confirma existencia y título "Poesía" y aporta metadatos adicionales; cubre totalmente lo esperado.</t>
+          <t>Confirma existencia del artículo 'Poesía' y aporta metadatos; cubre exactamente lo esperado.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -16690,12 +16698,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0.009517</t>
+          <t>0.00955925</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -16751,22 +16759,22 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Sólo menciona el artículo "Escritor"; la esperada listaba 10 artículos distintos, por lo que falta la mayoría de entidades.</t>
+          <t>Indica que Shakespeare se menciona en 'Escritor' (incluido en la esperada) pero omite muchos otros artículos listados en la respuesta esperada.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -16776,12 +16784,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0.0094425</t>
+          <t>0.00948475</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -17029,7 +17037,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -17039,7 +17047,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real provee la lista completa (187) y los títulos tal como en la esperada; coincide plenamente.</t>
+          <t>Proporciona la lista completa (187 títulos) tal como en la respuesta esperada.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -17049,12 +17057,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>0.01713425</t>
+          <t>0.0171765</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -17146,7 +17154,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -17156,7 +17164,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Lista los 30 artículos y confirma el conteo; corresponde exactamente con la respuesta esperada.</t>
+          <t>Devuelve 30 artículos con desambiguadores, coincidiendo exactamente con la lista esperada.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -17166,12 +17174,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>0.0127215</t>
+          <t>0.01276375</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -17418,7 +17426,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -17428,7 +17436,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real entrega la lista exhaustiva de artículos (187) coincidente con la esperada.</t>
+          <t>Lista exhaustiva de 187 artículos, coincide con la respuesta esperada.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -17438,12 +17446,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0.01334325</t>
+          <t>0.0133855</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -17690,7 +17698,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -17700,7 +17708,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Proporciona el catálogo completo de 187 artículos, igual que la respuesta esperada.</t>
+          <t>Catálogo completo (187 títulos) presentado; responde exactamente a la petición.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -17710,12 +17718,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0.01064225</t>
+          <t>0.0106845</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -17776,7 +17784,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -17786,7 +17794,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye exactamente los tres artículos esperados bajo 'Novelas históricas'.</t>
+          <t>Los tres artículos solicitados aparecen tal como en la respuesta esperada.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -17796,12 +17804,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0.0108645</t>
+          <t>0.01090675</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -17863,22 +17871,22 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Contradice la esperada: reporta máximo 4 categorías compartidas y pares distintos, mientras que la esperada daba otro par con 6; información errónea.</t>
+          <t>Responde a la pregunta dando pares y un máximo de 4 categorías compartidas, pero difiere del par y del conteo (6) esperado.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -17888,12 +17896,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0.014821</t>
+          <t>0.01486325</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -17956,7 +17964,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -17966,7 +17974,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real enumera las mismas tres artículos asociados a la categoría 'Mujeres' que la esperada.</t>
+          <t>Lista los tres artículos bajo 'Mujeres' exactamente como en la respuesta esperada.</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -17976,12 +17984,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>0.00882625</t>
+          <t>0.0088685</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -18045,7 +18053,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -18055,7 +18063,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real lista exactamente 'Francisco López Martínez (pintor)' y 'Ultraísmo' como en la esperada.</t>
+          <t>Indica los dos artículos vinculados a 'Movimientos artísticos del siglo XX', coincidiendo con lo esperado.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -18065,12 +18073,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0.00050975</t>
+          <t>0.000552</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0.00993675</t>
+          <t>0.009979</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -18126,22 +18134,22 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>La esperada es True pero la respuesta afirma 'No'; contradicción total, omite la información requerida.</t>
+          <t>Responde directamente con 'No' pero contradice la respuesta esperada; responde a la pregunta aunque es incorrecta respecto al gold.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -18151,12 +18159,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>0.0101625</t>
+          <t>0.0101265</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -18217,17 +18225,17 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Coincide perfectamente: el artículo describe la Novísima poesía latinoamericana como 'un movimiento literario'.</t>
+          <t>Coincide exactamente: confirma la referencia a 'Movimiento literario' con cita literal; respuesta directa y pertinente.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -18237,12 +18245,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0.00911575</t>
+          <t>0.00907975</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -18310,17 +18318,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>La respuesta confirma la conexión conceptual entre ambos artículos y aporta detalle sobre categorías y alcance.</t>
+          <t>Afirma la conexión conceptual entre ambos artículos y explica ausencia de enlace metadata; cubre la información esperada y es relevante.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -18330,12 +18338,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0.010869</t>
+          <t>0.010833</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -18396,17 +18404,17 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Coincide: la bibliografía del artículo contiene la palabra 'antología' como indica la esperada.</t>
+          <t>Confirma la aparición de 'antología' en la bibliografía con referencia concreta; corresponde plenamente a la pregunta.</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -18416,12 +18424,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0.0091795</t>
+          <t>0.0091435</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -18490,17 +18498,17 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: la respuesta documenta la influencia y paralelismos entre la poesía hispanohebrea y la árabe.</t>
+          <t>Describe la relación cultural y formal entre ambas tradiciones y menciona el tema homoerótico; cumple y responde directamente.</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -18510,12 +18518,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0.01107475</t>
+          <t>0.01103875</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -18587,7 +18595,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
@@ -18597,7 +18605,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: mismos cinco artículos en el mismo orden y con los mismos recuentos de palabras.</t>
+          <t>Lista los cinco artículos en el mismo orden y aporta los recuentos de palabras coincidentes; respuesta completa y pertinente.</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -18607,12 +18615,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>0.00926825</t>
+          <t>0.00923225</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -18729,7 +18737,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
@@ -18739,7 +18747,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Aunque incluye muchos más, la lista real contiene todos los artículos esperados sobre movimientos literarios.</t>
+          <t>Incluye todos los artículos esperados (y más) como pertenecientes a la categoría 'Movimientos literarios'; responde exhaustivamente.</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -18749,12 +18757,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>0.01121425</t>
+          <t>0.01117825</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -18846,7 +18854,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -18856,7 +18864,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Coincide: reporta 30 títulos y proporciona el mismo listado de artículos que empieza por vocal mayúscula.</t>
+          <t>Cuenta 30 y lista los 30 títulos que comienzan por vocal mayúscula, coincidiendo con la respuesta esperada; respuesta directa y correcta.</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -18866,12 +18874,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>0.01482775</t>
+          <t>0.01479175</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
@@ -18932,12 +18940,12 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -18947,7 +18955,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>La respuesta solo lista 3 de los 14 artículos esperados (incluye 3 correctos pero omite la mayoría).</t>
+          <t>Solo lista 3 artículos cuando la lista esperada es más larga; las entradas proporcionadas son correctas pero la respuesta es incompleta.</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -18957,12 +18965,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0.0123895</t>
+          <t>0.0123535</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -19027,12 +19035,12 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -19042,7 +19050,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>La respuesta aporta 5 de los 14 artículos esperados; cubre varios correctos pero omite numerosos items clave.</t>
+          <t>Proporciona cinco artículos relevantes a la Segunda Guerra Mundial (todos válidos) pero omite varias entradas esperadas; respuesta parcial.</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -19052,12 +19060,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0.00047025</t>
+          <t>0.00043425</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>0.01207</t>
+          <t>0.012034</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -19114,12 +19122,12 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -19129,7 +19137,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Encontró solo 2 de 14 artículos esperados (Poesía visual; Revistas literarias del exilio español), omitiendo la gran mayoría.</t>
+          <t>Solo identifica 2 de las 14 entradas esperadas; acierta esas dos pero omite la mayoría de las entidades requeridas.</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -19139,12 +19147,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>0.010457</t>
+          <t>0.01053525</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -19203,12 +19211,12 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -19218,7 +19226,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Informe 2 artículos frente a 9 esperados (solo Boom y Nueva narrativa), por tanto cobertura muy parcial.</t>
+          <t>Informa que aparece en 2 artículos (ejemplos incluidos) pero difiere notablemente del conteo esperado (9). Respuesta directa pero incompleta.</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -19228,12 +19236,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>0.0105885</t>
+          <t>0.01066675</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
@@ -19295,22 +19303,22 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Reconoce relación temática entre ambos pero niega referencia mutua; la respuesta esperada pedía referencia explícita mutua.</t>
+          <t>No confirma referencia mutua explícita (contradice la esperada) pero ofrece análisis conceptual útil sobre la relación entre ambos artículos.</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -19320,12 +19328,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>0.01124975</t>
+          <t>0.011328</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
@@ -19389,7 +19397,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
@@ -19399,7 +19407,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Coincide plenamente: afirma y justifica la referencia bidireccional entre Boom latinoamericano y Post‑Boom.</t>
+          <t>Confirma bidireccionalidad y aporta citas textuales de ambos artículos que prueban la referencia mutua, coincide plenamente con lo esperado.</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -19409,12 +19417,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0.00946225</t>
+          <t>0.0095405</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr"/>
@@ -19471,22 +19479,22 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real indica 0 pares mientras la esperada da 21: error total u omisión grave.</t>
+          <t>Declara 0 pares mutuamente referenciados (muy distinto a 21), pero responde directamente y explica la limitación de los fragmentos analizados.</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -19496,12 +19504,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>0.0100615</t>
+          <t>0.01013975</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
@@ -19561,22 +19569,22 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>La esperada da un intermedio concreto (Escritor); la real afirma que no existe tal intermedio en el corpus.</t>
+          <t>Afirma que no existe artículo intermedio en el corpus; responde la pregunta aunque contradice la solución esperada que da 'Escritor'.</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -19586,12 +19594,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0.0118685</t>
+          <t>0.01194675</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
@@ -19649,12 +19657,12 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -19664,7 +19672,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Esperado: cadena vía 'Escritor'. Real propone 'Alchemised' por categorías, no coincide con la respuesta esperada.</t>
+          <t>Propone 'Alchemised' como nexo por categorías, que no coincide con la cadena esperada basada en menciones; responde pero no como solicitado.</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -19674,12 +19682,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>0.012365</t>
+          <t>0.01244325</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -19742,12 +19750,12 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
@@ -19757,7 +19765,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Incluye las categorías esperadas y añade una más ('Movimientos literarios'); casi coincide totalmente.</t>
+          <t>Lista todas las categorías esperadas y añade una más; cubre plenamente las categorías solicitadas.</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -19767,12 +19775,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>0.008947</t>
+          <t>0.00902525</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
@@ -19828,12 +19836,12 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -19843,7 +19851,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Incluye las cuatro categorías esperadas y añade 'Movimientos literarios'; corresponde en gran medida.</t>
+          <t>Incluye las cuatro categorías esperadas y una adicional; responde completa y directamente a la pregunta.</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -19853,12 +19861,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>0.00976925</t>
+          <t>0.0098475</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -19920,7 +19928,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -19930,7 +19938,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Esperado 'Abu Nuwas' (nombre propio). La real da un artículo/término distinto, no coincide.</t>
+          <t>Da un término en vez del nombre propio esperado (Abu Nuwas); respuesta incorrecta y no responde la pregunta pedida.</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -19940,12 +19948,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0.000363</t>
+          <t>0.00044125</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>0.01263125</t>
+          <t>0.0127095</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
